--- a/data/trans_camb/IP16B03-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16B03-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 62,52</t>
+          <t>-22,12; 63,18</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-22,24; 171,45</t>
+          <t>-22,16; 163,99</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-62,02; 0,0</t>
+          <t>-63,57; 0,0</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-62,02; 0,0</t>
+          <t>-63,57; 0,0</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 0,0</t>
+          <t>-51,48; 0,0</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-75,0; 0,0</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,55</t>
+          <t>0,0; 40,44</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,88</t>
+          <t>0,0; 36,2</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 8,71</t>
+          <t>-16,88; 8,69</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 8,75</t>
+          <t>-17,86; 8,49</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 0,0</t>
+          <t>-51,48; 0,0</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-75,0; 0,0</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,99</t>
+          <t>0,0; 68,54</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,0</t>
+          <t>0,0; 56,86</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 9,5</t>
+          <t>-16,93; 9,48</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 9,55</t>
+          <t>-18,33; 9,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B03-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16B03-Provincia-trans_camb.xlsx
@@ -1587,7 +1587,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 63,18</t>
+          <t>-22,17; 66,48</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-22,16; 163,99</t>
+          <t>-22,2; 163,99</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-63,57; 0,0</t>
+          <t>-76,14; 0,0</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-63,57; 0,0</t>
+          <t>-76,14; 0,0</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 0,0</t>
+          <t>-44,32; 0,0</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1889,22 +1889,22 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,44</t>
+          <t>0,0; 36,99</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,2</t>
+          <t>0,0; 37,63</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 8,69</t>
+          <t>-21,51; 8,79</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 8,49</t>
+          <t>-17,23; 8,77</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 0,0</t>
+          <t>-44,32; 0,0</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1965,22 +1965,22 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,54</t>
+          <t>0,0; 58,72</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,86</t>
+          <t>0,0; 60,33</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 9,48</t>
+          <t>-21,64; 9,57</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 9,28</t>
+          <t>-17,54; 9,6</t>
         </is>
       </c>
     </row>
